--- a/datasource/metadata/drama-author.xlsx
+++ b/datasource/metadata/drama-author.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/me/github/HuygensING/translatin/datasource/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3937D43E-82D3-394A-9BEE-B941CC6340F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92B5450E-A167-0E4F-ABA4-82A1A5FCD6F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="520" windowWidth="67160" windowHeight="37260" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="520" windowWidth="33580" windowHeight="37260" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="drama" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1679" uniqueCount="865">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1691" uniqueCount="868">
   <si>
     <t>title (short)</t>
   </si>
@@ -2707,6 +2707,15 @@
   </si>
   <si>
     <t>Castus</t>
+  </si>
+  <si>
+    <t>Sophompaneas</t>
+  </si>
+  <si>
+    <t>Lambertias</t>
+  </si>
+  <si>
+    <t>Ovis</t>
   </si>
 </sst>
 </file>
@@ -3032,7 +3041,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O119"/>
+  <dimension ref="A1:O122"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
@@ -4530,109 +4539,79 @@
         <v>1630</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="34">
+    <row r="36" spans="1:15" ht="17">
       <c r="A36" s="1" t="s">
-        <v>308</v>
+        <v>865</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>309</v>
+        <v>290</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>308</v>
+        <v>865</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>315</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I36" s="2">
-        <v>5</v>
-      </c>
-      <c r="J36" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="M36" s="2" t="s">
-        <v>317</v>
+        <v>865</v>
       </c>
     </row>
     <row r="37" spans="1:15" ht="34">
       <c r="A37" s="1" t="s">
-        <v>190</v>
+        <v>308</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>322</v>
+        <v>178</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>315</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>47</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="I37" s="2">
         <v>5</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="K37" s="2">
-        <v>1602</v>
+        <v>21</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>316</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>167</v>
+        <v>312</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="O37" s="2">
-        <v>1602</v>
+        <v>317</v>
       </c>
     </row>
     <row r="38" spans="1:15" ht="34">
       <c r="A38" s="1" t="s">
-        <v>328</v>
+        <v>190</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>320</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>321</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>47</v>
@@ -4647,36 +4626,36 @@
         <v>52</v>
       </c>
       <c r="K38" s="2">
-        <v>1632</v>
+        <v>1602</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>167</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="O38" s="2">
-        <v>1632</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="39" spans="1:15" ht="34">
       <c r="A39" s="1" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>47</v>
@@ -4691,33 +4670,36 @@
         <v>52</v>
       </c>
       <c r="K39" s="2">
-        <v>1656</v>
+        <v>1632</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>92</v>
+        <v>167</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="O39" s="2">
-        <v>1656</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="40" spans="1:15" ht="34">
       <c r="A40" s="1" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>334</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="D40" s="11" t="s">
-        <v>345</v>
+        <v>346</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>335</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>47</v>
@@ -4744,21 +4726,21 @@
         <v>1656</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="17">
+    <row r="41" spans="1:15" ht="34">
       <c r="A41" s="1" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>350</v>
+        <v>334</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>345</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>47</v>
@@ -4773,80 +4755,53 @@
         <v>52</v>
       </c>
       <c r="K41" s="2">
-        <v>1611</v>
+        <v>1656</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>167</v>
+        <v>92</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>352</v>
+        <v>337</v>
       </c>
       <c r="O41" s="2">
-        <v>1611</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" ht="34">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" ht="17">
       <c r="A42" s="1" t="s">
-        <v>423</v>
+        <v>866</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>419</v>
+        <v>334</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I42" s="2">
-        <v>3</v>
-      </c>
-      <c r="J42" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K42" s="2">
-        <v>1519</v>
-      </c>
-      <c r="L42" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="M42" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="O42" s="2">
-        <v>1519</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" ht="34">
+        <v>866</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" ht="17">
       <c r="A43" s="1" t="s">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>365</v>
+        <v>349</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>47</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>123</v>
+        <v>48</v>
       </c>
       <c r="I43" s="2">
         <v>5</v>
@@ -4855,33 +4810,33 @@
         <v>52</v>
       </c>
       <c r="K43" s="2">
-        <v>1575</v>
+        <v>1611</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>341</v>
+        <v>167</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>367</v>
+        <v>352</v>
       </c>
       <c r="O43" s="2">
-        <v>1575</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="44" spans="1:15" ht="34">
       <c r="A44" s="1" t="s">
-        <v>375</v>
+        <v>423</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>368</v>
+        <v>419</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>375</v>
+        <v>423</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>376</v>
+        <v>425</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>377</v>
+        <v>424</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>47</v>
@@ -4890,80 +4845,83 @@
         <v>20</v>
       </c>
       <c r="I44" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K44" s="2">
-        <v>1537</v>
+        <v>1519</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>382</v>
+        <v>426</v>
       </c>
       <c r="O44" s="2">
-        <v>1536</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" ht="17">
+        <v>1519</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" ht="34">
       <c r="A45" s="1" t="s">
-        <v>380</v>
+        <v>363</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>381</v>
+        <v>357</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>380</v>
+        <v>365</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>366</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>20</v>
+        <v>123</v>
       </c>
       <c r="I45" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="K45" s="2">
-        <v>1485</v>
+        <v>1575</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>378</v>
+        <v>341</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="O45" s="2">
-        <v>1485</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" ht="17">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" ht="34">
       <c r="A46" s="1" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>388</v>
+        <v>368</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>389</v>
+        <v>376</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>377</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>20</v>
@@ -4975,162 +4933,156 @@
         <v>21</v>
       </c>
       <c r="K46" s="2">
-        <v>1497</v>
-      </c>
-      <c r="N46" s="2" t="s">
-        <v>274</v>
+        <v>1537</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="M46" s="2" t="s">
+        <v>382</v>
       </c>
       <c r="O46" s="2">
-        <v>1497</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="47" spans="1:15" ht="17">
       <c r="A47" s="1" t="s">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>401</v>
+        <v>380</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>403</v>
+        <v>380</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>123</v>
+        <v>20</v>
       </c>
       <c r="I47" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="K47" s="2">
-        <v>1562</v>
+        <v>1485</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>69</v>
+        <v>378</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>404</v>
+        <v>379</v>
       </c>
       <c r="O47" s="2">
-        <v>1562</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="48" spans="1:15" ht="17">
       <c r="A48" s="1" t="s">
-        <v>839</v>
+        <v>387</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>405</v>
+        <v>387</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>406</v>
+        <v>387</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>389</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I48" s="2">
+        <v>0</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K48" s="2">
+        <v>1497</v>
+      </c>
+      <c r="N48" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="O48" s="2">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" ht="17">
+      <c r="A49" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="I49" s="2">
         <v>5</v>
       </c>
-      <c r="J48" s="2" t="s">
+      <c r="J49" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="K48" s="2">
-        <v>1565</v>
-      </c>
-      <c r="L48" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="M48" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="O48" s="2">
-        <v>1565</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" ht="51">
-      <c r="A49" s="1" t="s">
-        <v>840</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I49" s="2">
-        <v>4</v>
-      </c>
-      <c r="J49" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K49" s="2" t="s">
-        <v>412</v>
+      <c r="K49" s="2">
+        <v>1562</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>136</v>
+        <v>69</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="O49" s="2">
-        <v>1502</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="50" spans="1:15" ht="17">
       <c r="A50" s="1" t="s">
-        <v>729</v>
+        <v>839</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>430</v>
+        <v>394</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>730</v>
+        <v>405</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>730</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>727</v>
+        <v>405</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>726</v>
+        <v>406</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>47</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="I50" s="2">
         <v>5</v>
@@ -5139,71 +5091,71 @@
         <v>52</v>
       </c>
       <c r="K50" s="2">
-        <v>1628</v>
+        <v>1565</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>258</v>
+        <v>92</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>728</v>
+        <v>407</v>
       </c>
       <c r="O50" s="2">
-        <v>1622</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" ht="17">
+        <v>1565</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" ht="51">
       <c r="A51" s="1" t="s">
-        <v>427</v>
+        <v>840</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>428</v>
+        <v>408</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>429</v>
+        <v>409</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>431</v>
+        <v>411</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>47</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="I51" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="K51" s="2">
-        <v>1617</v>
+        <v>21</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>412</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>326</v>
+        <v>136</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>432</v>
+        <v>413</v>
       </c>
       <c r="O51" s="2">
-        <v>1617</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="52" spans="1:15" ht="17">
       <c r="A52" s="1" t="s">
-        <v>849</v>
+        <v>729</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>430</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>727</v>
@@ -5233,24 +5185,24 @@
         <v>728</v>
       </c>
       <c r="O52" s="2">
-        <v>1615</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="53" spans="1:15" ht="17">
       <c r="A53" s="1" t="s">
-        <v>841</v>
+        <v>427</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>430</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="F53" s="8" t="s">
-        <v>450</v>
+        <v>429</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>431</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>47</v>
@@ -5265,30 +5217,30 @@
         <v>52</v>
       </c>
       <c r="K53" s="2">
-        <v>1610</v>
+        <v>1617</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>326</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="O53" s="2">
-        <v>1610</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="54" spans="1:15" ht="17">
       <c r="A54" s="1" t="s">
-        <v>731</v>
+        <v>849</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>430</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>732</v>
+        <v>725</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>732</v>
+        <v>725</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>727</v>
@@ -5318,27 +5270,24 @@
         <v>728</v>
       </c>
       <c r="O54" s="2">
-        <v>1628</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="55" spans="1:15" ht="17">
       <c r="A55" s="1" t="s">
-        <v>733</v>
+        <v>841</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>430</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>734</v>
+        <v>439</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>727</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>726</v>
+        <v>440</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>450</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>47</v>
@@ -5353,30 +5302,30 @@
         <v>52</v>
       </c>
       <c r="K55" s="2">
-        <v>1628</v>
+        <v>1610</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>258</v>
+        <v>326</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>728</v>
+        <v>441</v>
       </c>
       <c r="O55" s="2">
-        <v>1625</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="56" spans="1:15" ht="17">
       <c r="A56" s="1" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>430</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>727</v>
@@ -5406,33 +5355,33 @@
         <v>728</v>
       </c>
       <c r="O56" s="2">
-        <v>1621</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15" ht="51">
+        <v>1628</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" ht="17">
       <c r="A57" s="1" t="s">
-        <v>449</v>
+        <v>733</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>454</v>
+        <v>734</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>455</v>
+        <v>734</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>451</v>
+        <v>727</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>452</v>
+        <v>726</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>47</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="I57" s="2">
         <v>5</v>
@@ -5441,42 +5390,42 @@
         <v>52</v>
       </c>
       <c r="K57" s="2">
-        <v>1552</v>
+        <v>1628</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>398</v>
+        <v>258</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>453</v>
+        <v>728</v>
       </c>
       <c r="O57" s="2">
-        <v>1551</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15" ht="34">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" ht="17">
       <c r="A58" s="1" t="s">
-        <v>456</v>
+        <v>735</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>457</v>
+        <v>736</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>458</v>
+        <v>736</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="F58" s="8" t="s">
-        <v>452</v>
+        <v>727</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>726</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>47</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="I58" s="2">
         <v>5</v>
@@ -5485,36 +5434,36 @@
         <v>52</v>
       </c>
       <c r="K58" s="2">
-        <v>1552</v>
+        <v>1628</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>398</v>
+        <v>258</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>453</v>
+        <v>728</v>
       </c>
       <c r="O58" s="2">
-        <v>1535</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" ht="34">
+        <v>1621</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" ht="51">
       <c r="A59" s="1" t="s">
-        <v>485</v>
+        <v>449</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>442</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>487</v>
+        <v>454</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>488</v>
+        <v>455</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>451</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>486</v>
+        <v>452</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>47</v>
@@ -5529,30 +5478,30 @@
         <v>52</v>
       </c>
       <c r="K59" s="2">
-        <v>1545</v>
+        <v>1552</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>92</v>
+        <v>398</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>426</v>
+        <v>453</v>
       </c>
       <c r="O59" s="2">
-        <v>1545</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" ht="17">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" ht="34">
       <c r="A60" s="1" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>442</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>451</v>
@@ -5582,27 +5531,27 @@
         <v>453</v>
       </c>
       <c r="O60" s="2">
-        <v>1537</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" ht="17">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" ht="34">
       <c r="A61" s="1" t="s">
-        <v>462</v>
+        <v>485</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>442</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>463</v>
+        <v>487</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>464</v>
+        <v>488</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>451</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>452</v>
+        <v>486</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>47</v>
@@ -5617,35 +5566,35 @@
         <v>52</v>
       </c>
       <c r="K61" s="2">
-        <v>1552</v>
+        <v>1545</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>398</v>
+        <v>92</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>453</v>
+        <v>426</v>
       </c>
       <c r="O61" s="2">
-        <v>1540</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" ht="51">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" ht="17">
       <c r="A62" s="1" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>442</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="F62" s="2" t="s">
+      <c r="F62" s="8" t="s">
         <v>452</v>
       </c>
       <c r="G62" s="2" t="s">
@@ -5670,21 +5619,21 @@
         <v>453</v>
       </c>
       <c r="O62" s="2">
-        <v>1539</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="63" spans="1:15" ht="17">
       <c r="A63" s="1" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>442</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>451</v>
@@ -5705,7 +5654,7 @@
         <v>52</v>
       </c>
       <c r="K63" s="2">
-        <v>1554</v>
+        <v>1552</v>
       </c>
       <c r="L63" s="2" t="s">
         <v>398</v>
@@ -5714,24 +5663,27 @@
         <v>453</v>
       </c>
       <c r="O63" s="2">
-        <v>1554</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15" ht="34">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" ht="51">
       <c r="A64" s="1" t="s">
-        <v>842</v>
+        <v>465</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>442</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>472</v>
+        <v>467</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>451</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>473</v>
+        <v>452</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>47</v>
@@ -5746,7 +5698,7 @@
         <v>52</v>
       </c>
       <c r="K64" s="2">
-        <v>1556</v>
+        <v>1552</v>
       </c>
       <c r="L64" s="2" t="s">
         <v>398</v>
@@ -5755,21 +5707,21 @@
         <v>453</v>
       </c>
       <c r="O64" s="2">
-        <v>1556</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="65" spans="1:15" ht="17">
       <c r="A65" s="1" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>442</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>451</v>
@@ -5790,7 +5742,7 @@
         <v>52</v>
       </c>
       <c r="K65" s="2">
-        <v>1552</v>
+        <v>1554</v>
       </c>
       <c r="L65" s="2" t="s">
         <v>398</v>
@@ -5799,27 +5751,24 @@
         <v>453</v>
       </c>
       <c r="O65" s="2">
-        <v>1544</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15" ht="17">
+        <v>1554</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" ht="34">
       <c r="A66" s="1" t="s">
-        <v>691</v>
+        <v>842</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>442</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>451</v>
+        <v>472</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>452</v>
+        <v>473</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>47</v>
@@ -5834,7 +5783,7 @@
         <v>52</v>
       </c>
       <c r="K66" s="2">
-        <v>1552</v>
+        <v>1556</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>398</v>
@@ -5843,21 +5792,21 @@
         <v>453</v>
       </c>
       <c r="O66" s="2">
-        <v>1541</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="67" spans="1:15" ht="17">
       <c r="A67" s="1" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>442</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>451</v>
@@ -5878,7 +5827,7 @@
         <v>52</v>
       </c>
       <c r="K67" s="2">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>398</v>
@@ -5887,21 +5836,21 @@
         <v>453</v>
       </c>
       <c r="O67" s="2">
-        <v>1536</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15" ht="34">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" ht="17">
       <c r="A68" s="1" t="s">
-        <v>482</v>
+        <v>691</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>442</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>451</v>
@@ -5931,33 +5880,33 @@
         <v>453</v>
       </c>
       <c r="O68" s="2">
-        <v>1535</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15" ht="34">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" ht="17">
       <c r="A69" s="1" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>491</v>
+        <v>442</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>490</v>
+        <v>479</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="F69" s="8" t="s">
-        <v>493</v>
+        <v>451</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>452</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>47</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="I69" s="2">
         <v>5</v>
@@ -5966,39 +5915,42 @@
         <v>52</v>
       </c>
       <c r="K69" s="2">
-        <v>1632</v>
+        <v>1553</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>92</v>
+        <v>398</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>494</v>
+        <v>453</v>
       </c>
       <c r="O69" s="2">
-        <v>1624</v>
-      </c>
-    </row>
-    <row r="70" spans="1:15" ht="17">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" ht="34">
       <c r="A70" s="1" t="s">
-        <v>843</v>
+        <v>482</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>500</v>
+        <v>442</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>506</v>
+        <v>484</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>506</v>
+        <v>483</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>451</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>507</v>
+        <v>452</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>47</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="I70" s="2">
         <v>5</v>
@@ -6007,36 +5959,36 @@
         <v>52</v>
       </c>
       <c r="K70" s="2">
-        <v>1591</v>
+        <v>1552</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>295</v>
+        <v>398</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>508</v>
+        <v>453</v>
       </c>
       <c r="O70" s="2">
-        <v>1545</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="71" spans="1:15" ht="34">
       <c r="A71" s="1" t="s">
-        <v>509</v>
+        <v>489</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>844</v>
+        <v>491</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>510</v>
+        <v>490</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>510</v>
+        <v>490</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>512</v>
+        <v>492</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>493</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>47</v>
@@ -6051,141 +6003,144 @@
         <v>52</v>
       </c>
       <c r="K71" s="2">
-        <v>1900</v>
+        <v>1632</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>393</v>
+        <v>92</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="N71" s="2" t="s">
-        <v>164</v>
+        <v>494</v>
       </c>
       <c r="O71" s="2">
-        <v>1314</v>
-      </c>
-    </row>
-    <row r="72" spans="1:15" ht="85">
+        <v>1624</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" ht="17">
       <c r="A72" s="1" t="s">
-        <v>862</v>
+        <v>843</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>526</v>
+        <v>500</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>523</v>
+        <v>506</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>525</v>
+        <v>506</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I72" s="2">
+        <v>5</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="K72" s="2">
+        <v>1591</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="M72" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="O72" s="2">
+        <v>1545</v>
       </c>
     </row>
     <row r="73" spans="1:15" ht="34">
       <c r="A73" s="1" t="s">
-        <v>527</v>
+        <v>509</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>530</v>
+        <v>844</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>528</v>
+        <v>510</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="F73" s="8" t="s">
-        <v>542</v>
+        <v>510</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>512</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>47</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="I73" s="2">
         <v>5</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="K73" s="2">
-        <v>1539</v>
+        <v>1900</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>92</v>
+        <v>393</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>531</v>
+        <v>513</v>
+      </c>
+      <c r="N73" s="2" t="s">
+        <v>164</v>
       </c>
       <c r="O73" s="2">
-        <v>1539</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15" ht="17">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" ht="85">
       <c r="A74" s="1" t="s">
-        <v>540</v>
+        <v>862</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>543</v>
+        <v>523</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="G74" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H74" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="I74" s="2">
-        <v>5</v>
-      </c>
-      <c r="J74" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="K74" s="2">
-        <v>1563</v>
-      </c>
-      <c r="L74" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="M74" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="O74" s="2">
-        <v>1563</v>
+        <v>524</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="75" spans="1:15" ht="34">
       <c r="A75" s="1" t="s">
-        <v>545</v>
+        <v>527</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>549</v>
+        <v>528</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>546</v>
+        <v>529</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>542</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>47</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>123</v>
+        <v>20</v>
       </c>
       <c r="I75" s="2">
         <v>5</v>
@@ -6194,156 +6149,156 @@
         <v>21</v>
       </c>
       <c r="K75" s="2">
-        <v>1546</v>
+        <v>1539</v>
       </c>
       <c r="L75" s="2" t="s">
         <v>92</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>547</v>
+        <v>531</v>
       </c>
       <c r="O75" s="2">
-        <v>1546</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="76" spans="1:15" ht="17">
       <c r="A76" s="1" t="s">
-        <v>845</v>
+        <v>540</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>551</v>
+        <v>535</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>553</v>
+        <v>541</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="I76" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="K76" s="2">
-        <v>1435</v>
+        <v>1563</v>
       </c>
       <c r="L76" s="2" t="s">
         <v>92</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>554</v>
+        <v>172</v>
       </c>
       <c r="O76" s="2">
-        <v>1435</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="77" spans="1:15" ht="34">
       <c r="A77" s="1" t="s">
-        <v>847</v>
+        <v>545</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>551</v>
+        <v>535</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>562</v>
+        <v>548</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>561</v>
+        <v>546</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>47</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>20</v>
+        <v>123</v>
       </c>
       <c r="I77" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K77" s="2">
-        <v>1534</v>
+        <v>1546</v>
       </c>
       <c r="L77" s="2" t="s">
         <v>92</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>563</v>
+        <v>547</v>
       </c>
       <c r="O77" s="2">
-        <v>1532</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="78" spans="1:15" ht="17">
       <c r="A78" s="1" t="s">
-        <v>564</v>
+        <v>845</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>551</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I78" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K78" s="2">
-        <v>1534</v>
+        <v>1435</v>
       </c>
       <c r="L78" s="2" t="s">
         <v>92</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>563</v>
+        <v>554</v>
       </c>
       <c r="O78" s="2">
-        <v>1532</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15" ht="17">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" ht="34">
       <c r="A79" s="1" t="s">
-        <v>566</v>
+        <v>847</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>568</v>
+        <v>551</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>577</v>
+        <v>562</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>47</v>
@@ -6352,42 +6307,39 @@
         <v>20</v>
       </c>
       <c r="I79" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="K79" s="2">
-        <v>1498</v>
+        <v>1534</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>180</v>
+        <v>92</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
       <c r="O79" s="2">
-        <v>1498</v>
-      </c>
-    </row>
-    <row r="80" spans="1:15" ht="34">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" ht="17">
       <c r="A80" s="1" t="s">
-        <v>578</v>
+        <v>564</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>568</v>
+        <v>551</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>579</v>
+        <v>564</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>580</v>
+        <v>565</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>581</v>
+        <v>561</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>47</v>
@@ -6396,39 +6348,39 @@
         <v>20</v>
       </c>
       <c r="I80" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K80" s="2">
-        <v>1504</v>
+        <v>1534</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>582</v>
+        <v>92</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>583</v>
+        <v>563</v>
       </c>
       <c r="O80" s="2">
-        <v>1504</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="81" spans="1:15" ht="17">
       <c r="A81" s="1" t="s">
-        <v>585</v>
+        <v>566</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>846</v>
+        <v>568</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>586</v>
+        <v>567</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>588</v>
+        <v>577</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>587</v>
+        <v>569</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>47</v>
@@ -6440,86 +6392,83 @@
         <v>5</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="K81" s="2">
-        <v>1599</v>
+        <v>1498</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>589</v>
+        <v>180</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>590</v>
+        <v>570</v>
       </c>
       <c r="O81" s="2">
-        <v>1599</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="82" spans="1:15" ht="34">
       <c r="A82" s="1" t="s">
-        <v>600</v>
+        <v>578</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>604</v>
+        <v>568</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>601</v>
+        <v>579</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>602</v>
+        <v>584</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="F82" s="8" t="s">
-        <v>603</v>
+        <v>580</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>581</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>47</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="I82" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="K82" s="2">
-        <v>1593</v>
+        <v>1504</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>258</v>
+        <v>582</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>622</v>
+        <v>583</v>
       </c>
       <c r="O82" s="2">
-        <v>1589</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="83" spans="1:15" ht="17">
       <c r="A83" s="1" t="s">
-        <v>609</v>
+        <v>585</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>610</v>
+        <v>846</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>609</v>
+        <v>586</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>224</v>
+        <v>588</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>611</v>
+        <v>587</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>20</v>
@@ -6531,33 +6480,36 @@
         <v>21</v>
       </c>
       <c r="K83" s="2">
-        <v>1615</v>
+        <v>1599</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>219</v>
+        <v>589</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>612</v>
+        <v>590</v>
       </c>
       <c r="O83" s="2">
-        <v>1615</v>
-      </c>
-    </row>
-    <row r="84" spans="1:15" ht="17">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" ht="34">
       <c r="A84" s="1" t="s">
-        <v>616</v>
+        <v>600</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>619</v>
+        <v>604</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>617</v>
+        <v>601</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="F84" s="2" t="s">
-        <v>620</v>
+        <v>602</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="F84" s="8" t="s">
+        <v>603</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>47</v>
@@ -6572,13 +6524,13 @@
         <v>52</v>
       </c>
       <c r="K84" s="2">
-        <v>1589</v>
+        <v>1593</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>97</v>
+        <v>258</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="O84" s="2">
         <v>1589</v>
@@ -6586,25 +6538,25 @@
     </row>
     <row r="85" spans="1:15" ht="17">
       <c r="A85" s="1" t="s">
-        <v>658</v>
+        <v>609</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>628</v>
+        <v>610</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>658</v>
+        <v>609</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>659</v>
+        <v>609</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>635</v>
+        <v>224</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>636</v>
+        <v>611</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>20</v>
@@ -6616,74 +6568,71 @@
         <v>21</v>
       </c>
       <c r="K85" s="2">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>49</v>
+        <v>219</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>637</v>
+        <v>612</v>
       </c>
       <c r="O85" s="2">
-        <v>1602</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="86" spans="1:15" ht="17">
       <c r="A86" s="1" t="s">
-        <v>660</v>
+        <v>616</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>628</v>
+        <v>619</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>660</v>
+        <v>617</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>635</v>
+        <v>618</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>636</v>
+        <v>620</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>47</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="I86" s="2">
         <v>5</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="K86" s="2">
-        <v>1614</v>
+        <v>1589</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>49</v>
+        <v>97</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>637</v>
+        <v>621</v>
       </c>
       <c r="O86" s="2">
-        <v>1603</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="87" spans="1:15" ht="17">
       <c r="A87" s="1" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>628</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>635</v>
@@ -6713,21 +6662,21 @@
         <v>637</v>
       </c>
       <c r="O87" s="2">
-        <v>1596</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="88" spans="1:15" ht="17">
       <c r="A88" s="1" t="s">
-        <v>647</v>
+        <v>660</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>628</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>647</v>
+        <v>660</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>648</v>
+        <v>661</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>635</v>
@@ -6757,21 +6706,21 @@
         <v>637</v>
       </c>
       <c r="O88" s="2">
-        <v>1596</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="89" spans="1:15" ht="17">
       <c r="A89" s="1" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>628</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>635</v>
@@ -6801,24 +6750,27 @@
         <v>637</v>
       </c>
       <c r="O89" s="2">
-        <v>1603</v>
-      </c>
-    </row>
-    <row r="90" spans="1:15" ht="34">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" ht="17">
       <c r="A90" s="1" t="s">
-        <v>848</v>
+        <v>647</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>628</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>670</v>
+        <v>647</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>671</v>
+        <v>648</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>635</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>672</v>
+        <v>636</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>47</v>
@@ -6833,30 +6785,30 @@
         <v>21</v>
       </c>
       <c r="K90" s="2">
-        <v>1607</v>
+        <v>1614</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>673</v>
+        <v>49</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>674</v>
+        <v>637</v>
       </c>
       <c r="O90" s="2">
-        <v>1607</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="91" spans="1:15" ht="17">
       <c r="A91" s="1" t="s">
-        <v>474</v>
+        <v>662</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>628</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>474</v>
+        <v>662</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>649</v>
+        <v>663</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>635</v>
@@ -6886,27 +6838,24 @@
         <v>637</v>
       </c>
       <c r="O91" s="2">
-        <v>1590</v>
-      </c>
-    </row>
-    <row r="92" spans="1:15" ht="17">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" ht="34">
       <c r="A92" s="1" t="s">
-        <v>646</v>
+        <v>848</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>628</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>646</v>
+        <v>670</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>635</v>
+        <v>671</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>636</v>
+        <v>672</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>47</v>
@@ -6921,30 +6870,30 @@
         <v>21</v>
       </c>
       <c r="K92" s="2">
-        <v>1614</v>
+        <v>1607</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>49</v>
+        <v>673</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>637</v>
+        <v>674</v>
       </c>
       <c r="O92" s="2">
-        <v>1592</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="93" spans="1:15" ht="17">
       <c r="A93" s="1" t="s">
-        <v>638</v>
+        <v>474</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>628</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>638</v>
+        <v>474</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>639</v>
+        <v>649</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>635</v>
@@ -6974,21 +6923,21 @@
         <v>637</v>
       </c>
       <c r="O93" s="2">
-        <v>1572</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="94" spans="1:15" ht="17">
       <c r="A94" s="1" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>628</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>635</v>
@@ -7018,21 +6967,21 @@
         <v>637</v>
       </c>
       <c r="O94" s="2">
-        <v>1570</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="95" spans="1:15" ht="17">
       <c r="A95" s="1" t="s">
-        <v>656</v>
+        <v>638</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>628</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>656</v>
+        <v>638</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>657</v>
+        <v>639</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>635</v>
@@ -7062,21 +7011,21 @@
         <v>637</v>
       </c>
       <c r="O95" s="2">
-        <v>1602</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="96" spans="1:15" ht="17">
       <c r="A96" s="1" t="s">
-        <v>664</v>
+        <v>642</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>628</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>664</v>
+        <v>642</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>667</v>
+        <v>643</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>635</v>
@@ -7106,21 +7055,21 @@
         <v>637</v>
       </c>
       <c r="O96" s="2">
-        <v>1592</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="97" spans="1:15" ht="17">
       <c r="A97" s="1" t="s">
-        <v>644</v>
+        <v>656</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>628</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>645</v>
+        <v>656</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>645</v>
+        <v>657</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>635</v>
@@ -7150,21 +7099,21 @@
         <v>637</v>
       </c>
       <c r="O97" s="2">
-        <v>1570</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="98" spans="1:15" ht="17">
       <c r="A98" s="1" t="s">
-        <v>564</v>
+        <v>664</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>628</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>564</v>
+        <v>664</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>651</v>
+        <v>667</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>635</v>
@@ -7194,21 +7143,21 @@
         <v>637</v>
       </c>
       <c r="O98" s="2">
-        <v>1599</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="99" spans="1:15" ht="17">
       <c r="A99" s="1" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>628</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>635</v>
@@ -7238,21 +7187,21 @@
         <v>637</v>
       </c>
       <c r="O99" s="2">
-        <v>1569</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="100" spans="1:15" ht="17">
       <c r="A100" s="1" t="s">
-        <v>863</v>
+        <v>564</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>628</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>652</v>
+        <v>564</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>635</v>
@@ -7287,16 +7236,16 @@
     </row>
     <row r="101" spans="1:15" ht="17">
       <c r="A101" s="1" t="s">
-        <v>654</v>
+        <v>640</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>628</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>654</v>
+        <v>640</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>655</v>
+        <v>641</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>635</v>
@@ -7326,21 +7275,21 @@
         <v>637</v>
       </c>
       <c r="O101" s="2">
-        <v>1602</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="102" spans="1:15" ht="17">
       <c r="A102" s="1" t="s">
-        <v>668</v>
+        <v>863</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>628</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>668</v>
+        <v>652</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>669</v>
+        <v>653</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>635</v>
@@ -7370,112 +7319,121 @@
         <v>637</v>
       </c>
       <c r="O102" s="2">
-        <v>1596</v>
-      </c>
-    </row>
-    <row r="103" spans="1:15" ht="34">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" ht="17">
       <c r="A103" s="1" t="s">
-        <v>676</v>
+        <v>654</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>675</v>
+        <v>628</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>677</v>
+        <v>654</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>684</v>
+        <v>655</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>678</v>
+        <v>635</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>679</v>
+        <v>636</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>47</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="I103" s="2">
         <v>5</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="K103" s="2">
-        <v>1562</v>
+        <v>1614</v>
       </c>
       <c r="L103" s="2" t="s">
         <v>49</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>680</v>
+        <v>637</v>
       </c>
       <c r="O103" s="2">
-        <v>1546</v>
-      </c>
-    </row>
-    <row r="104" spans="1:15" ht="34">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" ht="17">
       <c r="A104" s="1" t="s">
-        <v>864</v>
+        <v>668</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>688</v>
+        <v>628</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>687</v>
+        <v>668</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>687</v>
+        <v>669</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>635</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>689</v>
+        <v>636</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="H104" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I104" s="2">
+        <v>5</v>
+      </c>
+      <c r="J104" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K104" s="2">
+        <v>1614</v>
+      </c>
+      <c r="L104" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="M104" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="O104" s="2">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" ht="34">
+      <c r="A105" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H105" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="I104" s="2">
-        <v>0</v>
-      </c>
-      <c r="J104" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="K104" s="2">
-        <v>1587</v>
-      </c>
-      <c r="L104" s="2" t="s">
-        <v>690</v>
-      </c>
-      <c r="M104" s="2" t="s">
-        <v>691</v>
-      </c>
-      <c r="O104" s="2">
-        <v>1587</v>
-      </c>
-    </row>
-    <row r="105" spans="1:15" ht="17">
-      <c r="A105" s="1" t="s">
-        <v>703</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>702</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>704</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>704</v>
-      </c>
-      <c r="F105" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="G105" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H105" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="I105" s="2">
         <v>5</v>
@@ -7484,74 +7442,71 @@
         <v>52</v>
       </c>
       <c r="K105" s="2">
-        <v>1579</v>
+        <v>1562</v>
       </c>
       <c r="L105" s="2" t="s">
-        <v>700</v>
+        <v>49</v>
       </c>
       <c r="M105" s="2" t="s">
-        <v>706</v>
+        <v>680</v>
       </c>
       <c r="O105" s="2">
-        <v>1579</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="106" spans="1:15" ht="34">
       <c r="A106" s="1" t="s">
-        <v>707</v>
+        <v>864</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>702</v>
+        <v>688</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>707</v>
+        <v>687</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>709</v>
+        <v>687</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>708</v>
-      </c>
-      <c r="G106" s="2" t="s">
-        <v>47</v>
+        <v>689</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="I106" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J106" s="2" t="s">
         <v>52</v>
       </c>
       <c r="K106" s="2">
-        <v>1550</v>
+        <v>1587</v>
       </c>
       <c r="L106" s="2" t="s">
-        <v>710</v>
+        <v>690</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>711</v>
+        <v>691</v>
       </c>
       <c r="O106" s="2">
-        <v>1550</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="107" spans="1:15" ht="17">
       <c r="A107" s="1" t="s">
-        <v>712</v>
+        <v>703</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>714</v>
+        <v>702</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>712</v>
+        <v>704</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>713</v>
+        <v>704</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>715</v>
+        <v>705</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>47</v>
@@ -7563,42 +7518,42 @@
         <v>5</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="K107" s="2">
-        <v>1620</v>
+        <v>1579</v>
       </c>
       <c r="L107" s="2" t="s">
-        <v>92</v>
+        <v>700</v>
       </c>
       <c r="M107" s="2" t="s">
-        <v>716</v>
+        <v>706</v>
       </c>
       <c r="O107" s="2">
-        <v>1620</v>
-      </c>
-    </row>
-    <row r="108" spans="1:15" ht="51">
+        <v>1579</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" ht="34">
       <c r="A108" s="1" t="s">
-        <v>855</v>
+        <v>707</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>719</v>
+        <v>702</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>856</v>
+        <v>707</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>856</v>
+        <v>709</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>859</v>
+        <v>708</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>47</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="I108" s="2">
         <v>5</v>
@@ -7607,80 +7562,74 @@
         <v>52</v>
       </c>
       <c r="K108" s="2">
-        <v>1530</v>
+        <v>1550</v>
       </c>
       <c r="L108" s="2" t="s">
-        <v>857</v>
+        <v>710</v>
       </c>
       <c r="M108" s="2" t="s">
-        <v>858</v>
+        <v>711</v>
       </c>
       <c r="O108" s="2">
-        <v>1529</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="109" spans="1:15" ht="17">
       <c r="A109" s="1" t="s">
-        <v>744</v>
+        <v>712</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>737</v>
+        <v>714</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>745</v>
+        <v>712</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>745</v>
-      </c>
-      <c r="E109" s="2" t="s">
-        <v>742</v>
+        <v>713</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>743</v>
+        <v>715</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>47</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="I109" s="2">
         <v>5</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="K109" s="2">
-        <v>1656</v>
+        <v>1620</v>
       </c>
       <c r="L109" s="2" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="M109" s="2" t="s">
-        <v>746</v>
+        <v>716</v>
       </c>
       <c r="O109" s="2">
-        <v>1628</v>
-      </c>
-    </row>
-    <row r="110" spans="1:15" ht="17">
+        <v>1620</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" ht="51">
       <c r="A110" s="1" t="s">
-        <v>747</v>
+        <v>855</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>737</v>
+        <v>719</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>748</v>
+        <v>856</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>748</v>
-      </c>
-      <c r="E110" s="2" t="s">
-        <v>742</v>
+        <v>856</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>743</v>
+        <v>859</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>47</v>
@@ -7695,33 +7644,36 @@
         <v>52</v>
       </c>
       <c r="K110" s="2">
-        <v>1656</v>
+        <v>1530</v>
       </c>
       <c r="L110" s="2" t="s">
-        <v>69</v>
+        <v>857</v>
       </c>
       <c r="M110" s="2" t="s">
-        <v>746</v>
+        <v>858</v>
       </c>
       <c r="O110" s="2">
-        <v>1628</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="111" spans="1:15" ht="17">
       <c r="A111" s="1" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>737</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>751</v>
+        <v>745</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>742</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>752</v>
+        <v>743</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>47</v>
@@ -7736,33 +7688,36 @@
         <v>52</v>
       </c>
       <c r="K111" s="2">
-        <v>1610</v>
+        <v>1656</v>
       </c>
       <c r="L111" s="2" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="M111" s="2" t="s">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="O111" s="2">
-        <v>1610</v>
-      </c>
-    </row>
-    <row r="112" spans="1:15" ht="34">
+        <v>1628</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" ht="17">
       <c r="A112" s="1" t="s">
-        <v>850</v>
+        <v>747</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>737</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>755</v>
+        <v>748</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>742</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>756</v>
+        <v>743</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>47</v>
@@ -7777,36 +7732,33 @@
         <v>52</v>
       </c>
       <c r="K112" s="2">
-        <v>1624</v>
+        <v>1656</v>
       </c>
       <c r="L112" s="2" t="s">
         <v>69</v>
       </c>
       <c r="M112" s="2" t="s">
-        <v>757</v>
+        <v>746</v>
       </c>
       <c r="O112" s="2">
-        <v>1624</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="113" spans="1:15" ht="17">
       <c r="A113" s="1" t="s">
-        <v>111</v>
+        <v>750</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>737</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>749</v>
-      </c>
-      <c r="E113" s="2" t="s">
-        <v>742</v>
+        <v>751</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>743</v>
+        <v>752</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>47</v>
@@ -7821,39 +7773,39 @@
         <v>52</v>
       </c>
       <c r="K113" s="2">
-        <v>1656</v>
+        <v>1610</v>
       </c>
       <c r="L113" s="2" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="M113" s="2" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="O113" s="2">
-        <v>1623</v>
-      </c>
-    </row>
-    <row r="114" spans="1:15" ht="51">
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15" ht="34">
       <c r="A114" s="1" t="s">
-        <v>758</v>
+        <v>850</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>760</v>
+        <v>737</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>759</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>762</v>
+        <v>755</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>756</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>47</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="I114" s="2">
         <v>5</v>
@@ -7862,36 +7814,36 @@
         <v>52</v>
       </c>
       <c r="K114" s="2">
-        <v>1598</v>
-      </c>
-      <c r="L114" s="12" t="s">
-        <v>446</v>
+        <v>1624</v>
+      </c>
+      <c r="L114" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="M114" s="2" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="O114" s="2">
-        <v>1598</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="115" spans="1:15" ht="17">
       <c r="A115" s="1" t="s">
-        <v>851</v>
+        <v>111</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>765</v>
+        <v>737</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>763</v>
+        <v>749</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>764</v>
+        <v>749</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>766</v>
+        <v>742</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>767</v>
+        <v>743</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>47</v>
@@ -7906,74 +7858,77 @@
         <v>52</v>
       </c>
       <c r="K115" s="2">
-        <v>1758</v>
+        <v>1656</v>
       </c>
       <c r="L115" s="2" t="s">
-        <v>768</v>
+        <v>69</v>
       </c>
       <c r="M115" s="2" t="s">
-        <v>769</v>
+        <v>746</v>
       </c>
       <c r="O115" s="2">
-        <v>1758</v>
-      </c>
-    </row>
-    <row r="116" spans="1:15" ht="34">
+        <v>1623</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" ht="51">
       <c r="A116" s="1" t="s">
-        <v>779</v>
+        <v>758</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>852</v>
+        <v>760</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>780</v>
+        <v>758</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>781</v>
-      </c>
-      <c r="F116" s="2" t="s">
-        <v>782</v>
+        <v>759</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>762</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I116" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J116" s="2" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="K116" s="2">
-        <v>1495</v>
-      </c>
-      <c r="L116" s="2" t="s">
-        <v>776</v>
+        <v>1598</v>
+      </c>
+      <c r="L116" s="12" t="s">
+        <v>446</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>783</v>
+        <v>761</v>
       </c>
       <c r="O116" s="2">
-        <v>1494</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="117" spans="1:15" ht="17">
       <c r="A117" s="1" t="s">
-        <v>784</v>
+        <v>851</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>786</v>
+        <v>765</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>785</v>
+        <v>763</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>785</v>
+        <v>764</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>766</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>787</v>
+        <v>767</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>47</v>
@@ -7988,114 +7943,210 @@
         <v>52</v>
       </c>
       <c r="K117" s="2">
-        <v>1621</v>
+        <v>1758</v>
       </c>
       <c r="L117" s="2" t="s">
-        <v>326</v>
+        <v>768</v>
       </c>
       <c r="M117" s="2" t="s">
-        <v>788</v>
+        <v>769</v>
       </c>
       <c r="O117" s="2">
-        <v>1621</v>
-      </c>
-    </row>
-    <row r="118" spans="1:15" ht="51">
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15" ht="34">
       <c r="A118" s="1" t="s">
-        <v>800</v>
+        <v>779</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>794</v>
+        <v>852</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>801</v>
+        <v>780</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>802</v>
+        <v>781</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>803</v>
+        <v>782</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I118" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J118" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K118" s="2">
-        <v>1541</v>
+        <v>1495</v>
       </c>
       <c r="L118" s="2" t="s">
-        <v>49</v>
+        <v>776</v>
       </c>
       <c r="M118" s="2" t="s">
-        <v>280</v>
+        <v>783</v>
       </c>
       <c r="O118" s="2">
-        <v>1534</v>
-      </c>
-    </row>
-    <row r="119" spans="1:15" ht="34">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15" ht="17">
       <c r="A119" s="1" t="s">
-        <v>804</v>
+        <v>784</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>794</v>
+        <v>786</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>804</v>
+        <v>785</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>805</v>
+        <v>785</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>860</v>
+        <v>787</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>47</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="I119" s="2">
         <v>5</v>
       </c>
       <c r="J119" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="K119" s="2">
+        <v>1621</v>
+      </c>
+      <c r="L119" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="M119" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="O119" s="2">
+        <v>1621</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15" ht="51">
+      <c r="A120" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I120" s="2">
+        <v>5</v>
+      </c>
+      <c r="J120" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="K119" s="2">
+      <c r="K120" s="2">
+        <v>1541</v>
+      </c>
+      <c r="L120" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="M120" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="O120" s="2">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15" ht="17">
+      <c r="A121" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15" ht="34">
+      <c r="A122" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I122" s="2">
+        <v>5</v>
+      </c>
+      <c r="J122" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K122" s="2">
         <v>1533</v>
       </c>
-      <c r="L119" s="2" t="s">
+      <c r="L122" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="M119" s="2" t="s">
+      <c r="M122" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="O119" s="2">
+      <c r="O122" s="2">
         <v>1533</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O119">
-    <sortCondition ref="B2:B119"/>
-    <sortCondition ref="A2:A119"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O122">
+    <sortCondition ref="B2:B122"/>
+    <sortCondition ref="A2:A122"/>
   </sortState>
   <hyperlinks>
     <hyperlink ref="F4" r:id="rId1" display="https://mateo.uni-mannheim.de/camena/bald4/baldepoemata4.html" xr:uid="{91300F84-E18B-4EAD-96CD-536830FA4E4A}"/>
-    <hyperlink ref="F36" r:id="rId2" xr:uid="{B94FFA2F-42BD-4945-BE9D-E121C13D52EA}"/>
-    <hyperlink ref="F53" r:id="rId3" xr:uid="{A22DF038-CFCC-45C5-A40D-C9E5AD9293BE}"/>
-    <hyperlink ref="F58" r:id="rId4" xr:uid="{71EB0C37-4AA6-46D6-AC63-45EC4F02AE71}"/>
-    <hyperlink ref="F60" r:id="rId5" xr:uid="{34AA883A-1B47-4C05-B3A4-C6F4859323C1}"/>
-    <hyperlink ref="F69" r:id="rId6" xr:uid="{61A47655-FE82-4CE7-A820-5C0B9A5B927F}"/>
-    <hyperlink ref="F73" r:id="rId7" xr:uid="{0FFF656F-82FC-4581-845B-F9681E0C65C9}"/>
-    <hyperlink ref="F82" r:id="rId8" xr:uid="{F99B056E-1D46-44D0-A5A8-C7DF5248520F}"/>
+    <hyperlink ref="F37" r:id="rId2" xr:uid="{B94FFA2F-42BD-4945-BE9D-E121C13D52EA}"/>
+    <hyperlink ref="F55" r:id="rId3" xr:uid="{A22DF038-CFCC-45C5-A40D-C9E5AD9293BE}"/>
+    <hyperlink ref="F60" r:id="rId4" xr:uid="{71EB0C37-4AA6-46D6-AC63-45EC4F02AE71}"/>
+    <hyperlink ref="F62" r:id="rId5" xr:uid="{34AA883A-1B47-4C05-B3A4-C6F4859323C1}"/>
+    <hyperlink ref="F71" r:id="rId6" xr:uid="{61A47655-FE82-4CE7-A820-5C0B9A5B927F}"/>
+    <hyperlink ref="F75" r:id="rId7" xr:uid="{0FFF656F-82FC-4581-845B-F9681E0C65C9}"/>
+    <hyperlink ref="F84" r:id="rId8" xr:uid="{F99B056E-1D46-44D0-A5A8-C7DF5248520F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId9"/>
